--- a/output/full_scan/batch_seq0_2026-07-09.xlsx
+++ b/output/full_scan/batch_seq0_2026-07-09.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>945.6773700426986</v>
+        <v>1115.677370042699</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>295</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>61.06726544535778</v>
+        <v>61.0672654250592</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>28.03445372586074</v>
+        <v>28.03445373502565</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.45619479873511</v>
@@ -574,27 +574,27 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8383</v>
+        <v>8462</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>793.1340651944155</v>
+        <v>1009.237586363104</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>69.7</v>
+        <v>159</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>63.33356166312416</v>
+        <v>75.04497998437336</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>24.12719524053077</v>
+        <v>27.8280259257066</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.00425200349616</v>
+        <v>1.653985125323621</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4742187230159651</v>
+        <v>2.083721012579168</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8076</v>
+        <v>8383</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>695.1511446954252</v>
+        <v>993.1340651944156</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>26.55</v>
+        <v>69.7</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>59.18078371385995</v>
+        <v>63.33356162235251</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15.9487511431635</v>
+        <v>24.12719513228467</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.647438243884125</v>
+        <v>1.00425200349616</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.06497650705597351</v>
+        <v>0.4742187230159651</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>9912</v>
+        <v>8109</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>694.4366303811154</v>
+        <v>878.0023502984465</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>12.75</v>
+        <v>151</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>61.67959378512682</v>
+        <v>67.88999232222235</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>23.92313053705791</v>
+        <v>34.43542337584902</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.182956234191853</v>
+        <v>1.60023502984464</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.0251373501946395</v>
+        <v>3.696598794538755</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8109</v>
+        <v>8150</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>678.0023502984465</v>
+        <v>876.8387508265099</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>67.88999233765124</v>
+        <v>60.57725513729665</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>34.43542336678896</v>
+        <v>28.46799152065768</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.60023502984464</v>
+        <v>1.077232792477948</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,11 +782,11 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>3.696598794538755</v>
+        <v>0.7626856954733414</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>676.1884475010596</v>
+        <v>876.1884475010596</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>166.5</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>63.03026990782125</v>
+        <v>63.03026991290693</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>34.53291094273081</v>
+        <v>34.53291103471814</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>3.388772722792815</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2634657560898255</v>
+        <v>0.2634657556319357</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8071</v>
+        <v>8076</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>668.3630684226771</v>
+        <v>865.1511446954252</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>30.3</v>
+        <v>26.55</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>56.16952524295808</v>
+        <v>59.18078363967638</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45.72036670006163</v>
+        <v>15.94875114470185</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.3233409192416662</v>
+        <v>1.647438243884125</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.2045839526611312</v>
+        <v>0.0649765071036697</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8105</v>
+        <v>8050</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>663.1552652260657</v>
+        <v>852.8111485727704</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>20.25</v>
+        <v>58.2</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>46.86347190150864</v>
+        <v>59.31247361562337</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>29.30219950352414</v>
+        <v>28.43016010929973</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.2768883880371653</v>
+        <v>1.27672544648841</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.5192061369933623</v>
+        <v>0.3268032239343883</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8183</v>
+        <v>9912</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>661.0582718214687</v>
+        <v>804.4366303811153</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>33.25</v>
+        <v>12.75</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>50.50337920767885</v>
+        <v>61.67959383616773</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>25.71335393297694</v>
+        <v>23.92313053705791</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.993035921749817</v>
+        <v>0.182956234191853</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.0381944316655502</v>
+        <v>0.0251373501850988</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8462</v>
+        <v>8162</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>659.2375863631039</v>
+        <v>775.8476458495237</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>159</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>75.04497980778855</v>
+        <v>53.07435448246645</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>27.82802587448248</v>
+        <v>34.89908160736989</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.653985125323621</v>
+        <v>0.264644939977358</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>2.083721013246961</v>
+        <v>-0.8064447027978145</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8050</v>
+        <v>8105</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>652.8111485727704</v>
+        <v>773.1552652260657</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>58.2</v>
+        <v>20.25</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>59.31247366757641</v>
+        <v>46.86347190447598</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>28.43016011680585</v>
+        <v>29.30219949560802</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.27672544648841</v>
+        <v>0.2768883880371653</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.3268032238962304</v>
+        <v>-0.5192061370028991</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8150</v>
+        <v>8234</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>601.8387508265099</v>
+        <v>713.9801519859653</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>117</v>
+        <v>71.3</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>60.57725514192727</v>
+        <v>54.08842040254125</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>28.46799157053927</v>
+        <v>24.97210751898125</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.077232792477948</v>
+        <v>2.005055854556362</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.7626856954733414</v>
+        <v>0.496589600137444</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8234</v>
+        <v>8104</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>598.9801519859629</v>
+        <v>702.2650424804145</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>71.3</v>
+        <v>41.15</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>54.08842038031632</v>
+        <v>56.43581056018794</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>24.97210751898125</v>
+        <v>21.61414151330652</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.005055854556362</v>
+        <v>1.907303549848992</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.4965896002709996</v>
+        <v>0.1382028446536958</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8182</v>
+        <v>8476</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>592.8038785539248</v>
+        <v>682.9365488592482</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>51.9</v>
+        <v>24.1</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>52.65884568367183</v>
+        <v>69.47089172913357</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>28.45835264306294</v>
+        <v>52.66577772243522</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.2763535241656582</v>
+        <v>0.7843982169651426</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.2892111725484683</v>
+        <v>-0.1323091526819539</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8162</v>
+        <v>8464</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>585.8476458495237</v>
+        <v>673.8549248443123</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>360</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,49 +1294,49 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>53.07435501566896</v>
+        <v>55.43975572778834</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>34.89908296576309</v>
+        <v>24.4433042295841</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.264644939977358</v>
+        <v>0.2567285789561092</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.8064447094565281</v>
+        <v>0.5754967190019604</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8476</v>
+        <v>8071</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>572.9365488592482</v>
+        <v>668.3630684226771</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>24.1</v>
+        <v>30.3</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>69.47089176524119</v>
+        <v>56.16952523538243</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>52.66577769002939</v>
+        <v>45.72036671778669</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.7843982169651426</v>
+        <v>0.3233409192416662</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.132309152786892</v>
+        <v>-0.2045839526802115</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8104</v>
+        <v>8183</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>542.2650424804143</v>
+        <v>661.0582718214687</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>41.15</v>
+        <v>33.25</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>56.43581051800016</v>
+        <v>50.50337912858402</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>21.61414150850264</v>
+        <v>25.71335389062058</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.907303549848992</v>
+        <v>0.993035921749817</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.1382028447490959</v>
+        <v>0.0381944317323331</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8464</v>
+        <v>8131</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>538.8549248443123</v>
+        <v>659.7093205977966</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>360</v>
+        <v>76</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>55.4397558704833</v>
+        <v>54.23826064229602</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>24.44330422737657</v>
+        <v>15.3388544507352</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.2567285789561092</v>
+        <v>0.8061339364052358</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.5754967178571917</v>
+        <v>0.1372679883947489</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8121</v>
+        <v>8926</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>522.0392083563892</v>
+        <v>635.8410965429097</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>43.2</v>
+        <v>76</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>46.01205036682536</v>
+        <v>53.82908226239778</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>26.93569676554834</v>
+        <v>39.5236504734733</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.463380801481474</v>
+        <v>1.14384770345808</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,11 +1524,11 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-1.181001753970932</v>
+        <v>-0.8174598171576433</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>516.7835777267355</v>
+        <v>631.7835777267355</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>200.5</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>48.34554437276275</v>
+        <v>48.34554436383221</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>18.40773210335134</v>
+        <v>18.40773203929994</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0.60712301371217</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.6896527592124919</v>
+        <v>-0.6896527604526729</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8081</v>
+        <v>8454</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>516.6670399846553</v>
+        <v>628.2818728554798</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>43.46929511952799</v>
+        <v>42.55370537408209</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>22.0366733229449</v>
+        <v>30.79734963103905</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.7522557183279575</v>
+        <v>0.2583806430719161</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,11 +1630,11 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-4.13963262622323</v>
+        <v>-10.91133361180517</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>515.6891056147315</v>
+        <v>625.6891056147315</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>17.45</v>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>64.16934906090063</v>
+        <v>64.16934901692926</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>29.27648597438505</v>
+        <v>29.27648595709468</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0.6010255157362058</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.1281838479346911</v>
+        <v>0.1281838479442344</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9105</v>
+        <v>8932</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>504.6692033785012</v>
+        <v>620.9725387451867</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>8.640000000000001</v>
+        <v>118.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>44.23754771611613</v>
+        <v>64.73073799438365</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>27.65321361759424</v>
+        <v>27.80362776401319</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.5120132634931288</v>
+        <v>1.171700675291908</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,11 +1736,11 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.2056653028227542</v>
+        <v>1.240354152805631</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>504.1989739874781</v>
+        <v>619.1989739874781</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>26.65</v>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>44.55844367696022</v>
+        <v>44.55844366675031</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>24.57580056257041</v>
+        <v>24.57580064183846</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>0.2483687623525244</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.1500298183372479</v>
+        <v>-0.1500298183086287</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8438</v>
+        <v>9802</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>503.7258915209789</v>
+        <v>610.9543310785876</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>93.8</v>
+        <v>75</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>50.29320829783348</v>
+        <v>49.01220909140135</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>31.29009082782434</v>
+        <v>14.37176583233303</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.2948900313668285</v>
+        <v>1.103062369841868</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.1004685706267443</v>
+        <v>0.0135594259747029</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, stronger_than_market, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8289</v>
+        <v>8442</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>500.517649556419</v>
+        <v>609.6538802343662</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>60</v>
+        <v>45.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>45.41929945460027</v>
+        <v>64.41895286016253</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>16.95716432649959</v>
+        <v>33.12440180990393</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.3743715474824172</v>
+        <v>4.721176524104051</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.5328858195603164</v>
+        <v>0.7040531937606305</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8454</v>
+        <v>8411</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>498.2818728554798</v>
+        <v>607.9917372516737</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>268</v>
+        <v>12.4</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>42.55370538207916</v>
+        <v>59.22150848388524</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>30.79734965447398</v>
+        <v>28.16404869199081</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.2583806430719161</v>
+        <v>0.4169477617897513</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-10.9113336114236</v>
+        <v>0.0416734931157261</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8261</v>
+        <v>8072</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>496.5135795504086</v>
+        <v>603.945613912904</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>325</v>
+        <v>29.1</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>69.12892754832444</v>
+        <v>49.75038314894202</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>55.44570923669914</v>
+        <v>23.07041102456413</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.2084490089682444</v>
+        <v>0.6182587270784728</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>6.768753150818448</v>
+        <v>-0.119676299257613</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8070</v>
+        <v>8182</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>491.8138890204934</v>
+        <v>592.8038785539248</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>52.7</v>
+        <v>51.9</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>44.50315986077437</v>
+        <v>52.65884567163982</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>20.12881681601988</v>
+        <v>28.45835264306293</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.2704515978439559</v>
+        <v>0.2763535241656582</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.5621335074887485</v>
+        <v>-0.2892111724912283</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8222</v>
+        <v>8481</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>464.1610035544257</v>
+        <v>590.1883057571742</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>40</v>
+        <v>42.2</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>55.78887692518681</v>
+        <v>61.7168262738461</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>26.36029122375098</v>
+        <v>15.6148045455568</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.31610035544257</v>
+        <v>0.8518301106496419</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,11 +2107,11 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.4386204956211728</v>
+        <v>0.0190051480953711</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>455.8715182320715</v>
+        <v>570.8715182320715</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>20</v>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>53.33827538540674</v>
+        <v>53.33827529796323</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>10.51034578994613</v>
+        <v>10.51034566321763</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.5203770150877088</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.1004607201013469</v>
+        <v>0.1004607199869004</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8390</v>
+        <v>8271</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>451.6492273970744</v>
+        <v>570.2158623476537</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>102.5</v>
+        <v>181</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,49 +2195,49 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>39.8455681008874</v>
+        <v>36.45686885021827</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>22.2112703100469</v>
+        <v>21.90427900235503</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.75780993864456</v>
+        <v>0.6642569736882401</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.9962421091283916</v>
+        <v>-1.387063597796885</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8155</v>
+        <v>8222</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>443.8083508744366</v>
+        <v>549.1610035544256</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>351</v>
+        <v>40</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>38.63541560418516</v>
+        <v>55.78887695256027</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>16.96978174600641</v>
+        <v>26.36029128893332</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.377267328177039</v>
+        <v>1.31610035544257</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-3.421022029379353</v>
+        <v>0.4386204952395864</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8163</v>
+        <v>8422</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>436.4164762611074</v>
+        <v>540.7413506207932</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>37.15</v>
+        <v>27</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>41.14875973202361</v>
+        <v>43.27185008523418</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>27.9719530142982</v>
+        <v>11.93216930313512</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3694129225323225</v>
+        <v>0.4554102803392013</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.93893959794441</v>
+        <v>-0.1245269089168926</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8088</v>
+        <v>8438</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>433.6183151572999</v>
+        <v>533.7258915209784</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>56.2</v>
+        <v>93.8</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>40.06334434816122</v>
+        <v>50.29320822945643</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>17.80948447842077</v>
+        <v>31.29009068832885</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.3403442143233098</v>
+        <v>0.2948900313668285</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-1.24201179607869</v>
+        <v>-0.1004685700352765</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8064</v>
+        <v>8482</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>431.3049542737243</v>
+        <v>531.9391508083992</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>138</v>
+        <v>47.9</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>48.80343254462551</v>
+        <v>51.45796785955595</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>20.69688628400946</v>
+        <v>6.269655553446864</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.6552702426647457</v>
+        <v>0.6127540404887044</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-2.733976776753629</v>
+        <v>1.64649851323988</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8358</v>
+        <v>8070</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>431.0772677941344</v>
+        <v>531.8138890204934</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>533</v>
+        <v>52.7</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,49 +2460,49 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>44.44763701088688</v>
+        <v>44.50315980686903</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>14.16918452681902</v>
+        <v>20.12881691158162</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.002682781510087</v>
+        <v>0.2704515978439559</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-15.9421061112901</v>
+        <v>-0.5621335072884186</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8473</v>
+        <v>9910</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>429.7523090657825</v>
+        <v>527.9522720695777</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>45.6</v>
+        <v>67.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,49 +2513,49 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>41.23394138638199</v>
+        <v>40.16177495285331</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>21.05372351001992</v>
+        <v>18.52953395759014</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.2939152473461782</v>
+        <v>0.1530523833674873</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.8893133984406904</v>
+        <v>-0.5172554894174577</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, invest_trust_buy_2d, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8411</v>
+        <v>8404</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>427.9917372516737</v>
+        <v>527.7442166421383</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>12.4</v>
+        <v>16.8</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>59.22150843638472</v>
+        <v>50.26715444580545</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>28.1640488064969</v>
+        <v>12.21180761654493</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.4169477617897513</v>
+        <v>0.5193784433633225</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.0416734931157261</v>
+        <v>0.033262970118366</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8926</v>
+        <v>8367</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>425.8410965429097</v>
+        <v>523.1335717368592</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>76</v>
+        <v>40.6</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>53.82908225467781</v>
+        <v>51.4640411736636</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>39.5236504427654</v>
+        <v>23.05793382485463</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.14384770345808</v>
+        <v>0.6651478707831056</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.8174598172434937</v>
+        <v>0.0958519428134709</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8072</v>
+        <v>8121</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>423.9456139129026</v>
+        <v>522.0392083563892</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>29.1</v>
+        <v>43.2</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>49.75038296544552</v>
+        <v>46.01205036821492</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>23.07041086146804</v>
+        <v>26.93569678601256</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6182587270784728</v>
+        <v>0.463380801481474</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.1196762989046417</v>
+        <v>-1.18100175396139</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8227</v>
+        <v>8499</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>423.6712131124241</v>
+        <v>518.2127134373869</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>185.5</v>
+        <v>296.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45.80306717624389</v>
+        <v>47.93131713816332</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>12.99532340291337</v>
+        <v>14.79822053702875</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.649614603709303</v>
+        <v>0.5617447962911463</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.5525161769779747</v>
+        <v>-1.054488043331421</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8932</v>
+        <v>9904</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>420.9725387451866</v>
+        <v>516.8135305664756</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>118.5</v>
+        <v>24.25</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,49 +2778,49 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>64.73073796243801</v>
+        <v>30.033248098473</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>27.80362789161046</v>
+        <v>22.87504677792818</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.171700675291908</v>
+        <v>0.6054744714400423</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M44" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>1.240354153296111</v>
+        <v>-0.1401728044730671</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8131</v>
+        <v>8114</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>419.7093205977965</v>
+        <v>511.7745063088752</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>76</v>
+        <v>204</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>54.23826064821935</v>
+        <v>48.53987379318993</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>15.33885450202597</v>
+        <v>20.96956477275687</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.8061339364052358</v>
+        <v>0.6604384438484757</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.1372679884042944</v>
+        <v>2.066539990810189</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8271</v>
+        <v>9908</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>415.2158623476537</v>
+        <v>511.2046478050366</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>181</v>
+        <v>29.75</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>36.45686885143411</v>
+        <v>53.95161250287389</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>21.90427902917804</v>
+        <v>21.18261677063101</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.6642569736882401</v>
+        <v>0.4738728805535227</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-1.387063597777805</v>
+        <v>0.0083044872770497</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8443</v>
+        <v>8081</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>412.5002513771728</v>
+        <v>506.6670399846552</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>11.4</v>
+        <v>283</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,49 +2937,49 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>46.13949241805911</v>
+        <v>43.46929510127833</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>44.73439615055887</v>
+        <v>22.03667335040938</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.0481716894679872</v>
+        <v>0.7522557183279575</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0057353044910645</v>
+        <v>-4.139632626318647</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8481</v>
+        <v>9105</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>410.1883057571743</v>
+        <v>504.6692033785012</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>42.2</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>61.71682619664692</v>
+        <v>44.23754774298521</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>15.61480457483754</v>
+        <v>27.65321369698066</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.8518301106496419</v>
+        <v>0.5120132634931288</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0190051481049095</v>
+        <v>-0.2056653028437405</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8215</v>
+        <v>8289</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>405.5732340568613</v>
+        <v>500.517649556419</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>28.3</v>
+        <v>60</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>45.71331973782882</v>
+        <v>45.41929945012008</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>20.61677245725222</v>
+        <v>16.95716428647348</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.2766731409496856</v>
+        <v>0.3743715474824172</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.2392043864600765</v>
+        <v>-0.5328858195603164</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8176</v>
+        <v>8443</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>399.7922122566903</v>
+        <v>497.5002513771721</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>10.3</v>
+        <v>11.4</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>49.71103299719211</v>
+        <v>46.13949251823645</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>21.97176157443163</v>
+        <v>44.73439621384803</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.5831018499189248</v>
+        <v>0.0481716894679872</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0275414278138644</v>
+        <v>0.0057353044815238</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8240</v>
+        <v>8261</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>395.2113740577323</v>
+        <v>496.5135795504086</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>48.8</v>
+        <v>325</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>33.09307695295985</v>
+        <v>69.12892754832444</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>17.26048881949011</v>
+        <v>55.44570923669914</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.498376104229703</v>
+        <v>0.2084490089682444</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.282133747353948</v>
+        <v>6.768753150818448</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>9905</v>
+        <v>8163</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>394.7291682637969</v>
+        <v>496.4164762611074</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>20.3</v>
+        <v>37.15</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>29.97470606341192</v>
+        <v>41.14875970625288</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>25.19298520073606</v>
+        <v>27.97195300628072</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.243391772090515</v>
+        <v>0.3694129225323225</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.0454726360808902</v>
+        <v>-0.9389395979253284</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>9802</v>
+        <v>8147</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>385.9543310785877</v>
+        <v>495.1816317860768</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>75</v>
+        <v>148.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>49.01220913370903</v>
+        <v>46.16509233734722</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>14.37176585357015</v>
+        <v>17.62618890485057</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.103062369841868</v>
+        <v>0.5878523398230003</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0135594268332919</v>
+        <v>1.58414472079184</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8367</v>
+        <v>8084</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>383.1335717368591</v>
+        <v>488.9207580125134</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>40.6</v>
+        <v>48.4</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>51.46404127481393</v>
+        <v>50.72814826575077</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>23.05793373091461</v>
+        <v>18.02611738711937</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.6651478707831056</v>
+        <v>1.088735107192531</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.09585194271807811</v>
+        <v>-0.1675966924043465</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8147</v>
+        <v>9902</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>380.1816317860768</v>
+        <v>487.623777832203</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>148.5</v>
+        <v>13.9</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>46.16509233734722</v>
+        <v>51.73246758487272</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>17.62618895281261</v>
+        <v>16.95341081796073</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5878523398230003</v>
+        <v>0.6921889327884256</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>1.584144720982638</v>
+        <v>0.0427060187768476</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8084</v>
+        <v>8102</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>373.9207580125134</v>
+        <v>471.3815513040738</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>48.4</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>50.7281484383933</v>
+        <v>47.56714087540008</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>18.02611738711937</v>
+        <v>19.78887841127128</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.088735107192531</v>
+        <v>0.49273110642548</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.1675966923471095</v>
+        <v>-0.4311246219099497</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>9908</v>
+        <v>8299</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>371.2046478050366</v>
+        <v>469.0565057878965</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>29.75</v>
+        <v>2220</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,49 +3467,49 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>53.95161254900417</v>
+        <v>44.96039061681675</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>21.18261677063101</v>
+        <v>11.59840834354179</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4738728805535227</v>
+        <v>0.7347657251072689</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0083044872675095</v>
+        <v>-26.47269659297076</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8442</v>
+        <v>8390</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>369.6538802343663</v>
+        <v>451.6492273970744</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>45.5</v>
+        <v>102.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>64.41895290474335</v>
+        <v>39.84556806597796</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>33.12440183567698</v>
+        <v>22.21127028568718</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>4.721176524104051</v>
+        <v>0.75780993864456</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.7040531937987955</v>
+        <v>-0.996242108994838</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>9136</v>
+        <v>8473</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>362.2078982861705</v>
+        <v>449.7523090657825</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>12.55</v>
+        <v>45.6</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>42.58474468158637</v>
+        <v>41.23394133066769</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>28.72398115359664</v>
+        <v>21.05372349597616</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.3196330501566053</v>
+        <v>0.2939152473461782</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.6419772183503466</v>
+        <v>-0.8893133983262131</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8422</v>
+        <v>8215</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>360.7413506207933</v>
+        <v>445.5732340568613</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>27</v>
+        <v>28.3</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>43.27184999914081</v>
+        <v>45.71331970282166</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>11.93216925376998</v>
+        <v>20.61677251347744</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.4554102803392013</v>
+        <v>0.2766731409496856</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.1245269092438809</v>
+        <v>-0.2392043862883598</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8299</v>
+        <v>8155</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>354.0565057878965</v>
+        <v>443.8083508744366</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>2220</v>
+        <v>351</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,49 +3679,49 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>44.96039062390757</v>
+        <v>38.63541559122939</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>11.59840828976886</v>
+        <v>16.96978183309137</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.7347657251072689</v>
+        <v>0.377267328177039</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-26.47269659392488</v>
+        <v>-3.421022029570119</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8291</v>
+        <v>9905</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>351.7285087794172</v>
+        <v>434.729168263797</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>31.3</v>
+        <v>20.3</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>32.08781306874354</v>
+        <v>29.97470607376064</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>28.64617609887791</v>
+        <v>25.19298514904185</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.2513839144264409</v>
+        <v>1.243391772090515</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-1.065056303544633</v>
+        <v>-0.0454726360904279</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8114</v>
+        <v>8088</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>341.7745063088752</v>
+        <v>433.6183151572998</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>204</v>
+        <v>56.2</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>48.53987393122882</v>
+        <v>40.06334435151384</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>20.96956461547611</v>
+        <v>17.8094844955883</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.6604384438484757</v>
+        <v>0.3403442143233098</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>2.06653998861605</v>
+        <v>-1.24201179632673</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8499</v>
+        <v>9911</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>338.2127134373869</v>
+        <v>432.8594704106036</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>296.5</v>
+        <v>83.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>47.93131715325546</v>
+        <v>49.77914693572831</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>14.79822048841337</v>
+        <v>12.77942880661165</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5617447962911463</v>
+        <v>0.4639707539751356</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-1.054488043713031</v>
+        <v>0.0380759908806658</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8110</v>
+        <v>8064</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>337.6101091997573</v>
+        <v>431.3049542737243</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>50.6</v>
+        <v>138</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>41.27964155117965</v>
+        <v>48.8034325358894</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>14.05885536949449</v>
+        <v>20.69688626070109</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.314151785716672</v>
+        <v>0.6552702426647457</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.9634335027095274</v>
+        <v>-2.733976776744095</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8996</v>
+        <v>8358</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>335.8373916738241</v>
+        <v>431.0772677941343</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>1230</v>
+        <v>533</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,49 +3944,49 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>43.51256971700781</v>
+        <v>44.44763701001893</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>17.84660428053814</v>
+        <v>14.16918453333716</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.9166473883185942</v>
+        <v>1.002682781510087</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-34.10953469623792</v>
+        <v>-15.94210611138548</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8102</v>
+        <v>8467</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>331.3815513040738</v>
+        <v>424.247507293484</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>68.40000000000001</v>
+        <v>114.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>47.56714098362745</v>
+        <v>47.4478619430393</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>19.78887828267896</v>
+        <v>10.19427519484404</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.49273110642548</v>
+        <v>0.7403179957687805</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.4311246223869271</v>
+        <v>0.2481098240923858</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8374</v>
+        <v>8227</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>318.2076840377574</v>
+        <v>423.6712131124241</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>85.8</v>
+        <v>185.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>43.07833635130708</v>
+        <v>45.80306714521925</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>12.01040259944046</v>
+        <v>12.99532338878422</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5755238588886022</v>
+        <v>0.649614603709303</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.1270594985555098</v>
+        <v>-0.5525161769779747</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8103</v>
+        <v>8487</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>317.7345067709381</v>
+        <v>421.4675632926595</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>92</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>39.88218166092185</v>
+        <v>48.9020716185816</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>14.67310478493414</v>
+        <v>10.2602300443176</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6481509532312247</v>
+        <v>1.073099012897976</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.2073250878073955</v>
+        <v>-0.0396687258315949</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8455</v>
+        <v>8176</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>302.105947900884</v>
+        <v>399.7922122566903</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>26.7</v>
+        <v>10.3</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>39.84813827271169</v>
+        <v>49.71103299719211</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.47522053956229</v>
+        <v>21.97176163383466</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.0392972813818824</v>
+        <v>0.5831018499189248</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.1485431495417388</v>
+        <v>0.0275414278043245</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>9110</v>
+        <v>8472</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>296.7953652063451</v>
+        <v>398.5207344755143</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>49.66149296689225</v>
+        <v>46.20172078990742</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>10.88735982732729</v>
+        <v>14.64293840787254</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>3.792195355518314</v>
+        <v>0.1479566726818865</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0422966925918032</v>
+        <v>-0.7978961380693976</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8074</v>
+        <v>8240</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>295.8880411465574</v>
+        <v>395.2113740577323</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>63.3</v>
+        <v>48.8</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>37.87450463105208</v>
+        <v>33.09307693918753</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>15.15794763636885</v>
+        <v>17.26048879343706</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4143264025013059</v>
+        <v>0.498376104229703</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.6000948286237189</v>
+        <v>-0.2821337473825687</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>9906</v>
+        <v>9907</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>欣巴巴</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>292.143673660012</v>
+        <v>384.8723125461834</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>40.5</v>
+        <v>15.1</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>46.82952773427228</v>
+        <v>37.63123704515055</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>32.10037881483254</v>
+        <v>25.41310071195872</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.1771634003716415</v>
+        <v>0.4092549006427862</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.4400113480687876</v>
+        <v>0.0039432378089251</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8086</v>
+        <v>8478</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>285.6239169596563</v>
+        <v>378.3473488122249</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>38.76691700234044</v>
+        <v>48.12161167179845</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>13.75482811658706</v>
+        <v>16.89352377524925</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5730116599568847</v>
+        <v>0.3991303168051845</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-1.675103492196563</v>
+        <v>0.6545073135075389</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8277</v>
+        <v>8110</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>283.3755703830312</v>
+        <v>377.6101091997573</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>36.20151374817589</v>
+        <v>41.27964154609241</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>25.24125625102812</v>
+        <v>14.05885539589013</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.09308290079936</v>
+        <v>0.314151785716672</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.301293470047814</v>
+        <v>-0.9634335027286028</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8111</v>
+        <v>8996</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>283.2561822382896</v>
+        <v>375.9005870503961</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>50.3</v>
+        <v>1230</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>32.868336113171</v>
+        <v>43.51256972829313</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>22.79305789173377</v>
+        <v>17.84660423307414</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.5490644012150034</v>
+        <v>0.92562443931219</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.08458687977787829</v>
+        <v>-34.10953469747805</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8067</v>
+        <v>8423</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>283.0989332374504</v>
+        <v>369.2987704211915</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>12.85</v>
+        <v>17.85</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>49.15975174108894</v>
+        <v>53.3668459353444</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>6.929793140172296</v>
+        <v>13.28746042316834</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.553056518671317</v>
+        <v>0.3173847257470447</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.098243353769288</v>
+        <v>0.0208541333579024</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>9911</v>
+        <v>8085</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>282.8594704106036</v>
+        <v>363.6389795293937</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>83.5</v>
+        <v>12.05</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>49.77914686426568</v>
+        <v>46.17014779080897</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>12.77942880707736</v>
+        <v>15.63279282068448</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.4639707539751356</v>
+        <v>0.7004860142280618</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0380759909379054</v>
+        <v>0.0032626563426619</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>9907</v>
+        <v>9136</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>274.8723125461834</v>
+        <v>362.2078982861704</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>15.1</v>
+        <v>12.55</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>37.63123705999909</v>
+        <v>42.58474468074567</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>25.41310058084437</v>
+        <v>28.72398116339357</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.4092549006427862</v>
+        <v>0.3196330501566053</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0039432377803053</v>
+        <v>-0.6419772183637033</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8054</v>
+        <v>8341</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>271.0985230027185</v>
+        <v>358.2256058067413</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>99</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>39.89613077241647</v>
+        <v>44.05032640970989</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>19.5229538368604</v>
+        <v>17.4629141703363</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.4020619072397809</v>
+        <v>0.4899590447223314</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-2.367327142856035</v>
+        <v>-0.2290720071413257</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8478</v>
+        <v>8374</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>268.3473488122247</v>
+        <v>358.2076840377573</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>154</v>
+        <v>85.8</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>48.12161187762693</v>
+        <v>43.07833640330028</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>16.89352377161159</v>
+        <v>12.01040259944046</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.3991303168051845</v>
+        <v>0.5755238588886022</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.6545073123627742</v>
+        <v>-0.1270594990325007</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>9902</v>
+        <v>8103</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>267.6237778322437</v>
+        <v>357.7345067709381</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>13.9</v>
+        <v>92</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>51.73246775716086</v>
+        <v>39.8821816632117</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>16.95341064822981</v>
+        <v>14.67310479726708</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.6921889327884256</v>
+        <v>0.6481509532312247</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0427060184906553</v>
+        <v>-0.207325087840102</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, cci_momentum</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8482</v>
+        <v>8291</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>266.9391508083992</v>
+        <v>351.7285087794172</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>47.9</v>
+        <v>31.3</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>51.45796785869525</v>
+        <v>32.0880296384428</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>6.269655576024899</v>
+        <v>28.64361429193721</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.6127540404887044</v>
+        <v>0.2513839144264409</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>1.64649851327804</v>
+        <v>-1.065058493400244</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8487</v>
+        <v>8087</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>261.4675632926595</v>
+        <v>350.2381185092995</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>78.59999999999999</v>
+        <v>31.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>48.90207158318503</v>
+        <v>39.51201307036008</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>10.26023001355993</v>
+        <v>9.939761454085946</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.073099012897976</v>
+        <v>0.1334495346187039</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0396687256408047</v>
+        <v>-0.1778934018084783</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8472</v>
+        <v>9955</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>258.5207344755142</v>
+        <v>342.8374489274156</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>80.40000000000001</v>
+        <v>26.2</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>46.20172080999976</v>
+        <v>39.63840763318574</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>14.64293840740606</v>
+        <v>21.05721512686502</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.1479566726818865</v>
+        <v>0.5969621450877978</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.7978961381838654</v>
+        <v>0.0526024647777393</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8404</v>
+        <v>8080</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>257.7442166421387</v>
+        <v>338.0395871849736</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>16.8</v>
+        <v>27.65</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>50.26715443284135</v>
+        <v>45.23047732231178</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>12.21180757921045</v>
+        <v>44.46316696331351</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5193784433633225</v>
+        <v>0.50996118408931</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0332629701851433</v>
+        <v>-0.0353434144483245</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8210</v>
+        <v>8089</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>255.9713515545421</v>
+        <v>335.4274160264428</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>1175</v>
+        <v>20.15</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>37.32978479712484</v>
+        <v>46.17930189133142</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>15.96238876500028</v>
+        <v>29.81126389929956</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.5168414934085372</v>
+        <v>1.087363777485494</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-16.78939741839588</v>
+        <v>0.0379194509400662</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8112</v>
+        <v>8048</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>242.2162939918141</v>
+        <v>334.2229420767324</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>85</v>
+        <v>60.3</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>39.62033749413564</v>
+        <v>42.551150356666</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>17.35161618081739</v>
+        <v>11.24031560884708</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.3607960075820646</v>
+        <v>0.3848596307198769</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-1.305692542055596</v>
+        <v>-0.4681051809288913</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>9904</v>
+        <v>9906</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>欣巴巴</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>241.8135305664756</v>
+        <v>332.1436736600119</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>24.25</v>
+        <v>40.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>30.03324830543582</v>
+        <v>46.82952767927328</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>22.87504677792817</v>
+        <v>32.10037882114131</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6054744714400423</v>
+        <v>0.1771634003716415</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.1401728044826101</v>
+        <v>-0.4400113481260208</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8087</v>
+        <v>8097</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>235.2381185092994</v>
+        <v>325.659380458411</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>31.5</v>
+        <v>57.2</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>39.51201305723559</v>
+        <v>44.90413513338844</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>9.939761445675153</v>
+        <v>15.99763298662898</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.1334495346187039</v>
+        <v>0.4244393338648179</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.1778934017893958</v>
+        <v>-0.3664628591442034</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8423</v>
+        <v>8463</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>229.2987704211915</v>
+        <v>318.9754446765962</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>17.85</v>
+        <v>21.4</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>53.36684595815468</v>
+        <v>43.74698482508509</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>13.2874604717595</v>
+        <v>11.62892780448736</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.3173847257470447</v>
+        <v>0.6620334290153785</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0208541333483638</v>
+        <v>0.0226175282223426</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, cci_momentum</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>9955</v>
+        <v>8201</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>227.8374489274156</v>
+        <v>310.8768255558915</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>26.2</v>
+        <v>12.65</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>39.63840759823555</v>
+        <v>42.25903746979009</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>21.057215132844</v>
+        <v>17.12761967338611</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.5969621450877978</v>
+        <v>0.7805358119190815</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0526024647681973</v>
+        <v>-0.0483359294584681</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8488</v>
+        <v>8455</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>225.5772379382442</v>
+        <v>302.105947900884</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>10.05</v>
+        <v>26.7</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>51.38842443844852</v>
+        <v>39.84813826912784</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>12.853580611973</v>
+        <v>17.47522052586842</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.1046525368942769</v>
+        <v>0.0392972813818824</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.1119711016724378</v>
+        <v>-0.1485431495417388</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8085</v>
+        <v>8440</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>223.6389795293937</v>
+        <v>299.6002125176242</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>12.05</v>
+        <v>21.15</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>46.17014781890236</v>
+        <v>40.81389033777026</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>15.63279302806912</v>
+        <v>8.921524531235683</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.7004860142280618</v>
+        <v>0.8820468167239903</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0032626563903607</v>
+        <v>-0.0310343616641632</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>9930</v>
+        <v>8112</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>223.6190157616402</v>
+        <v>297.2162939918141</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>63.4</v>
+        <v>85</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>26.03080374633542</v>
+        <v>39.62033749767727</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>40.94415587196991</v>
+        <v>17.35161616391018</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.9255205963591576</v>
+        <v>0.3607960075820646</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.4247382283239149</v>
+        <v>-1.305692542265477</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8048</v>
+        <v>9110</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>219.2229420767324</v>
+        <v>296.7953652063451</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>60.3</v>
+        <v>3</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>42.55115038065586</v>
+        <v>49.661492388719</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>11.24031565701613</v>
+        <v>10.8873601368843</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.3848596307198769</v>
+        <v>3.792195355518313</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.4681051809861264</v>
+        <v>0.0422966938205196</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8097</v>
+        <v>8210</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>210.6593804584109</v>
+        <v>295.971351554542</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>57.2</v>
+        <v>1175</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>44.90413512689214</v>
+        <v>37.32978479220419</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>15.99763294746235</v>
+        <v>15.96238883130079</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.4244393338648179</v>
+        <v>0.5168414934085372</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.3664628590488018</v>
+        <v>-16.78939741868191</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8080</v>
+        <v>8074</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>198.0395871849736</v>
+        <v>295.8880411465574</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>27.65</v>
+        <v>63.3</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>45.23047736060722</v>
+        <v>37.8745046288069</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>44.46316696394368</v>
+        <v>15.1579476418245</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.50996118408931</v>
+        <v>0.4143264025013059</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0353434144769411</v>
+        <v>-0.6000948286141834</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8068</v>
+        <v>8086</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>197.5962593156098</v>
+        <v>285.6239169596563</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>18.35</v>
+        <v>136</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>39.97609884766082</v>
+        <v>38.76691698832725</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>15.82079033379296</v>
+        <v>13.75482810374441</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.3570242923885193</v>
+        <v>0.5730116599568847</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0367244660194286</v>
+        <v>-1.675103492234736</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8213</v>
+        <v>8277</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>195.628965743694</v>
+        <v>283.3755703830312</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>34.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>36.65109372268826</v>
+        <v>36.20151372621674</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>15.24252182888576</v>
+        <v>25.24125623053746</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.7323996087380523</v>
+        <v>1.09308290079936</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.2100843902348135</v>
+        <v>-0.3012934700382736</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8089</v>
+        <v>9103</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>195.4274160264428</v>
+        <v>283.3570354182627</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>20.15</v>
+        <v>5.05</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>46.1793019489565</v>
+        <v>42.75236205455828</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>29.81126391234136</v>
+        <v>14.77643015652625</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.087363777485494</v>
+        <v>0.2751806063616129</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0379194510163846</v>
+        <v>-0.0327521483139481</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8440</v>
+        <v>8111</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>184.6002125176242</v>
+        <v>283.2561822382896</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>21.15</v>
+        <v>50.3</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>40.8138903099928</v>
+        <v>32.8683360740304</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>8.92152441622947</v>
+        <v>22.79305786866706</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.8820468167239903</v>
+        <v>0.5490644012150034</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0310343617691008</v>
+        <v>0.0845868798160376</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8463</v>
+        <v>8067</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>178.9754446765963</v>
+        <v>283.0989332374504</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>21.4</v>
+        <v>12.85</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>43.74698488851641</v>
+        <v>49.15975089255</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>11.62892781815846</v>
+        <v>6.929793138481662</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.6620334290153785</v>
+        <v>1.553056518671317</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0226175282032634</v>
+        <v>-0.098243353769288</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8341</v>
+        <v>8054</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>178.2256058067413</v>
+        <v>271.0985230027184</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>76.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>44.0503264398149</v>
+        <v>39.89613063782667</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>17.46291416702502</v>
+        <v>19.52295384602932</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.4899590447223314</v>
+        <v>0.4020619072397809</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.2290720071985575</v>
+        <v>-2.367327141444157</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8467</v>
+        <v>8477</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>174.247507293484</v>
+        <v>266.5488343633314</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>114.5</v>
+        <v>16.15</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>47.44786197850391</v>
+        <v>43.90362160694996</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>10.19427527848047</v>
+        <v>16.00308623562717</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.7403179957687805</v>
+        <v>0.8653098347675346</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.2481098242831847</v>
+        <v>-0.126517501899625</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8059</v>
+        <v>8488</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>173.5608444226128</v>
+        <v>265.5772379382442</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>15.85</v>
+        <v>10.05</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>31.47814877280417</v>
+        <v>51.38842442787487</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>22.74842880791754</v>
+        <v>12.85358078336584</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.6182104996544648</v>
+        <v>0.1046525368942769</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0069722023583087</v>
+        <v>0.1119711017010574</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>9103</v>
+        <v>8410</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>168.3570354182627</v>
+        <v>258.9399037878679</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>5.05</v>
+        <v>32.7</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>42.75236186717041</v>
+        <v>40.97192498423479</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>14.77643011734152</v>
+        <v>14.3393698133052</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.2751806063616129</v>
+        <v>0.0725773046257298</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0327521483501992</v>
+        <v>0.0505804742704311</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>9910</v>
+        <v>8429</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>157.9522720695777</v>
+        <v>254.2066594670316</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>67.5</v>
+        <v>6.25</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>40.16177496363483</v>
+        <v>42.91362816356017</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>18.52953391776828</v>
+        <v>14.06317849861863</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.1530523833674873</v>
+        <v>0.4069447824710997</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.5172554892266576</v>
+        <v>-0.0037274348734333</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8201</v>
+        <v>8940</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>155.8768255558915</v>
+        <v>250.2937797377582</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>12.65</v>
+        <v>16.35</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>42.25903753675748</v>
+        <v>42.20475450771418</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>17.12761967338611</v>
+        <v>17.4056076228492</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.7805358119190815</v>
+        <v>0.6937759516342598</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0483359294775492</v>
+        <v>0.0057510086171152</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8410</v>
+        <v>8092</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>143.939903787868</v>
+        <v>244.9355010277615</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>32.7</v>
+        <v>13.85</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>40.97192497163726</v>
+        <v>39.67721010738541</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>14.3393698133052</v>
+        <v>16.13650132012954</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.0725773046257298</v>
+        <v>0.4591774895810996</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0505804743658239</v>
+        <v>0.08258098117574569</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8940</v>
+        <v>9930</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>135.2937797377586</v>
+        <v>243.6190157616403</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>16.35</v>
+        <v>63.4</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>42.20475471624045</v>
+        <v>26.03080383499133</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.40560761392834</v>
+        <v>40.94415599853207</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.6937759516342598</v>
+        <v>0.9255205963591576</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0057510085503364</v>
+        <v>-0.4247382283620751</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8477</v>
+        <v>8171</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>126.5488343633314</v>
+        <v>239.6175117117485</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>16.15</v>
+        <v>20.5</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>43.90362167366214</v>
+        <v>39.98337630709346</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>16.00308621850667</v>
+        <v>19.45898394036229</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.8653098347675346</v>
+        <v>0.2094313273974103</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.126517501899625</v>
+        <v>-0.0012176860172278</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8171</v>
+        <v>8213</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>124.6175117117485</v>
+        <v>235.628965743694</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>20.5</v>
+        <v>34.1</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>39.98337632517716</v>
+        <v>36.65109367533598</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>19.45898398981927</v>
+        <v>15.24252183392751</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.2094313273974103</v>
+        <v>0.7323996087380523</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0012176860458439</v>
+        <v>-0.2100843901680322</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8249</v>
+        <v>8101</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>117.793979276608</v>
+        <v>201.0222525421475</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>47</v>
+        <v>13.1</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>38.22781073841121</v>
+        <v>43.8109976928297</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>14.80341977923104</v>
+        <v>11.87492375242674</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.3520585957571375</v>
+        <v>1.249848372903411</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.2080123321482176</v>
+        <v>-0.1094593490322934</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>8101</v>
+        <v>8068</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>116.0222525421475</v>
+        <v>197.5962593156099</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>13.1</v>
+        <v>18.35</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>43.81099779414703</v>
+        <v>39.97609880908545</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>11.87492378608344</v>
+        <v>15.82079035846971</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.249848372903411</v>
+        <v>0.3570242923885193</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.1094593491086123</v>
+        <v>0.0367244659335707</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,21 +6569,21 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>8429</v>
+        <v>8059</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>114.2066594670316</v>
+        <v>173.5608444226129</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>6.25</v>
+        <v>15.85</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>42.91362839755762</v>
+        <v>31.47814873665854</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>14.06317842663415</v>
+        <v>22.748428805081</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.4069447824710997</v>
+        <v>0.6182104996544648</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0037274348925124</v>
+        <v>-0.0069722024823228</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>8431</v>
+        <v>8249</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>85.28779323824058</v>
+        <v>87.79397927660796</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>49.35</v>
+        <v>47</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>37.82642006380287</v>
+        <v>38.22781080998095</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>10.60002882768182</v>
+        <v>14.80341979858149</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.6424411702082883</v>
+        <v>0.3520585957571375</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.1463169813488058</v>
+        <v>-0.2080123321386859</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6675,21 +6675,21 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>8092</v>
+        <v>8431</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>74.93550102776156</v>
+        <v>85.28779323824058</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>13.85</v>
+        <v>49.35</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>39.67721004386019</v>
+        <v>37.82642006380287</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>16.13650135571223</v>
+        <v>10.60002877873389</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.4591774895810996</v>
+        <v>0.6424411702082883</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.08258098139516031</v>
+        <v>-0.1463169817113161</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
